--- a/collection/template-export-forms.xlsx
+++ b/collection/template-export-forms.xlsx
@@ -1100,7 +1100,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Microsoft Forms export template for framework v2 (2.0.1).</t>
+          <t>Microsoft Forms export template for framework v2 (2.0.2).</t>
         </is>
       </c>
     </row>
